--- a/temp/template_allowance.xlsx
+++ b/temp/template_allowance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mizuno\Dailyreport_test\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC81FA99-67F6-4F71-9657-F808FE4C6AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40589722-2374-4B7B-99B1-1C0B067EA82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="135" windowWidth="23805" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="540" windowWidth="25605" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="宿泊" sheetId="34" r:id="rId1"/>
@@ -172,7 +172,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.0_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="179" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -384,7 +384,16 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -393,16 +402,7 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -755,17 +755,17 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="12" width="11.875" style="1" customWidth="1"/>
+    <col min="2" max="12" width="11.375" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="16"/>
+      <c r="A1" s="15"/>
       <c r="B1" s="9"/>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="13" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="10"/>
@@ -778,7 +778,7 @@
       <c r="L1" s="11"/>
     </row>
     <row r="2" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="17"/>
+      <c r="A2" s="16"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
       <c r="D2" s="3"/>
@@ -795,497 +795,497 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
     </row>
     <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
@@ -1369,17 +1369,17 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="12" width="11.875" style="1" customWidth="1"/>
+    <col min="2" max="12" width="11.25" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="14"/>
+      <c r="A1" s="17"/>
       <c r="B1" s="9"/>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="10"/>
@@ -1392,7 +1392,7 @@
       <c r="L1" s="11"/>
     </row>
     <row r="2" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="15"/>
+      <c r="A2" s="18"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
       <c r="D2" s="3"/>
@@ -1409,497 +1409,497 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
     </row>
     <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">

--- a/temp/template_allowance.xlsx
+++ b/temp/template_allowance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mizuno\Dailyreport_test\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5204D327-BAD8-4737-95B8-E98B267E49B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BB172D-A1C8-4D84-A50A-1D6451D2B80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="285" windowWidth="28815" windowHeight="15150" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29160" yWindow="120" windowWidth="28815" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="宿泊" sheetId="34" r:id="rId1"/>

--- a/temp/template_allowance.xlsx
+++ b/temp/template_allowance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mizuno\Dailyreport_test\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BB172D-A1C8-4D84-A50A-1D6451D2B80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B24299-3D80-4815-900D-4DF2FE9F2D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29160" yWindow="120" windowWidth="28815" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="27735" windowHeight="15150" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="宿泊" sheetId="34" r:id="rId1"/>
